--- a/data/projects/56A0TXN/早期介入/交付预案/解析结果/预案草稿/11.验收策略.xlsx
+++ b/data/projects/56A0TXN/早期介入/交付预案/解析结果/预案草稿/11.验收策略.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,40 +461,268 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>安装PAC</t>
+          <t>到货</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>方案A</t>
+          <t>设备到货清点</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>标准A</t>
+          <t>型号/数量与 BOQ 一致，外观无损</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>到货签收</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>DocA</t>
+          <t>到货验收单</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>到货</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>安装 PAC</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>整机柜 ST 测试</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>GPU 数量与 BOQ 一致，误码率 ≤ 1e-12</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>部署调测完成</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>验收测试报告</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>里程碑A</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>安装 PAC</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>安装 PAC</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>RDMA 全互联压测</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>400G 带宽达标，时延 p99 ≤ 2μs</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>集群联调完成</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>网络测试报告</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>维保</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>维保服务启动</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>维保策略与 SLA 合同一致</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>维保生效</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>维保确认函</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>培训</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AI 使能培训</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>参训人数 ≥ 合同，考核通过</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>培训完成</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>培训签到表</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>安装 PAC</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>整体性能基线</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>RTO ≤ 5s / p99 ≤ 30ms</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>整体压测完成</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>性能基线报告</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>终验</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>安装 PAC</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>客户签收移交</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>文档齐套，客户代表签字</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>客户验收</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>移交确认函</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>终验</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
